--- a/Team-Data/2008-09/3-19-2008-09.xlsx
+++ b/Team-Data/2008-09/3-19-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E2" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
         <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>0.594</v>
+        <v>0.588</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -688,7 +755,7 @@
         <v>7.3</v>
       </c>
       <c r="M2" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N2" t="n">
         <v>0.363</v>
@@ -700,7 +767,7 @@
         <v>25.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R2" t="n">
         <v>10.6</v>
@@ -712,7 +779,7 @@
         <v>40.2</v>
       </c>
       <c r="U2" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V2" t="n">
         <v>12.8</v>
@@ -736,19 +803,19 @@
         <v>98.40000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>29</v>
@@ -769,7 +836,7 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO2" t="n">
         <v>21</v>
@@ -793,13 +860,13 @@
         <v>17</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
         <v>12</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>8</v>
@@ -808,7 +875,7 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -843,64 +910,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
         <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>0.735</v>
+        <v>0.739</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J3" t="n">
         <v>77</v>
       </c>
       <c r="K3" t="n">
-        <v>0.487</v>
+        <v>0.486</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
         <v>16.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.392</v>
       </c>
       <c r="O3" t="n">
         <v>20.2</v>
       </c>
       <c r="P3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.773</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T3" t="n">
-        <v>42.5</v>
+        <v>42.4</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W3" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X3" t="n">
         <v>4.7</v>
@@ -909,19 +976,19 @@
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.6</v>
+        <v>101.4</v>
       </c>
       <c r="AC3" t="n">
         <v>8.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -933,7 +1000,7 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="n">
         <v>9</v>
@@ -951,7 +1018,7 @@
         <v>21</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO3" t="n">
         <v>8</v>
@@ -966,7 +1033,7 @@
         <v>18</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>8</v>
@@ -978,22 +1045,22 @@
         <v>29</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA3" t="n">
         <v>5</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1215,7 @@
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT4" t="n">
         <v>27</v>
@@ -1172,7 +1239,7 @@
         <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
         <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.456</v>
+        <v>0.464</v>
       </c>
       <c r="H5" t="n">
         <v>48.7</v>
       </c>
       <c r="I5" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J5" t="n">
-        <v>83.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
         <v>0.452</v>
@@ -1240,19 +1307,19 @@
         <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.791</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S5" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T5" t="n">
         <v>42.6</v>
@@ -1261,7 +1328,7 @@
         <v>20.8</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1276,16 +1343,16 @@
         <v>21.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1318,10 +1385,10 @@
         <v>6</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
@@ -1330,7 +1397,7 @@
         <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
         <v>7</v>
@@ -1339,7 +1406,7 @@
         <v>15</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
         <v>10</v>
@@ -1354,7 +1421,7 @@
         <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB5" t="n">
         <v>11</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -1392,40 +1459,40 @@
         <v>67</v>
       </c>
       <c r="E6" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.821</v>
+        <v>0.806</v>
       </c>
       <c r="H6" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J6" t="n">
-        <v>78.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="K6" t="n">
         <v>0.469</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
         <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.388</v>
+        <v>0.389</v>
       </c>
       <c r="O6" t="n">
         <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
         <v>0.754</v>
@@ -1440,34 +1507,34 @@
         <v>41.7</v>
       </c>
       <c r="U6" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="W6" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="X6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z6" t="n">
         <v>20</v>
       </c>
-      <c r="V6" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="X6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>20.1</v>
-      </c>
       <c r="AA6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1482,7 +1549,7 @@
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AJ6" t="n">
         <v>25</v>
@@ -1500,10 +1567,10 @@
         <v>3</v>
       </c>
       <c r="AO6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>24</v>
@@ -1512,7 +1579,7 @@
         <v>17</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>14</v>
@@ -1521,10 +1588,10 @@
         <v>24</v>
       </c>
       <c r="AV6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW6" t="n">
         <v>7</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>8</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
@@ -1533,10 +1600,10 @@
         <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB6" t="n">
         <v>12</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -1571,46 +1638,46 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" t="n">
         <v>41</v>
       </c>
       <c r="F7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>0.594</v>
+        <v>0.603</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J7" t="n">
-        <v>82.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L7" t="n">
         <v>6.9</v>
       </c>
       <c r="M7" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="O7" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P7" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>11.2</v>
@@ -1619,10 +1686,10 @@
         <v>31.6</v>
       </c>
       <c r="T7" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
         <v>13.1</v>
@@ -1634,22 +1701,22 @@
         <v>5.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA7" t="n">
         <v>20</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.2</v>
+        <v>101.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1670,16 +1737,16 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL7" t="n">
         <v>13</v>
       </c>
       <c r="AM7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO7" t="n">
         <v>24</v>
@@ -1691,19 +1758,19 @@
         <v>2</v>
       </c>
       <c r="AR7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS7" t="n">
         <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
         <v>16</v>
@@ -1721,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>7</v>
@@ -1846,10 +1913,10 @@
         <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1876,7 +1943,7 @@
         <v>13</v>
       </c>
       <c r="AS8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
         <v>13</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>16</v>
@@ -2043,7 +2110,7 @@
         <v>29</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2061,7 +2128,7 @@
         <v>18</v>
       </c>
       <c r="AT9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E10" t="n">
         <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>0.353</v>
+        <v>0.358</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
@@ -2135,7 +2202,7 @@
         <v>39.4</v>
       </c>
       <c r="J10" t="n">
-        <v>85.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K10" t="n">
         <v>0.459</v>
@@ -2144,16 +2211,16 @@
         <v>6.6</v>
       </c>
       <c r="M10" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O10" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="P10" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="Q10" t="n">
         <v>0.786</v>
@@ -2174,7 +2241,7 @@
         <v>15</v>
       </c>
       <c r="W10" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X10" t="n">
         <v>6.5</v>
@@ -2192,10 +2259,10 @@
         <v>108.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.6</v>
+        <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2207,7 +2274,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2249,19 +2316,19 @@
         <v>14</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2456,7 @@
         <v>6</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>27</v>
@@ -2425,7 +2492,7 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>19</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2571,7 +2638,7 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI12" t="n">
         <v>4</v>
@@ -2613,7 +2680,7 @@
         <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW12" t="n">
         <v>20</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="AH13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI13" t="n">
         <v>26</v>
@@ -2783,10 +2850,10 @@
         <v>27</v>
       </c>
       <c r="AR13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT13" t="n">
         <v>22</v>
@@ -2807,7 +2874,7 @@
         <v>23</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -2860,22 +2927,22 @@
         <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>40.8</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
-        <v>85.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O14" t="n">
         <v>19.9</v>
@@ -2887,7 +2954,7 @@
         <v>0.77</v>
       </c>
       <c r="R14" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S14" t="n">
         <v>31.7</v>
@@ -2896,10 +2963,10 @@
         <v>44.3</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V14" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
@@ -2914,16 +2981,16 @@
         <v>20.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.3</v>
+        <v>108</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2935,7 +3002,7 @@
         <v>2</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
         <v>2</v>
@@ -2953,7 +3020,7 @@
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO14" t="n">
         <v>9</v>
@@ -2968,7 +3035,7 @@
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2989,7 +3056,7 @@
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3141,7 +3208,7 @@
         <v>15</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3314,7 +3381,7 @@
         <v>11</v>
       </c>
       <c r="AM16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN16" t="n">
         <v>22</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17" t="n">
         <v>31</v>
       </c>
       <c r="F17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>0.449</v>
+        <v>0.443</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3412,22 +3479,22 @@
         <v>82.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L17" t="n">
         <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O17" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P17" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q17" t="n">
         <v>0.784</v>
@@ -3436,16 +3503,16 @@
         <v>12.1</v>
       </c>
       <c r="S17" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W17" t="n">
         <v>7.3</v>
@@ -3457,25 +3524,25 @@
         <v>4.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.7</v>
+        <v>-0.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
         <v>18</v>
@@ -3484,7 +3551,7 @@
         <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ17" t="n">
         <v>8</v>
@@ -3514,19 +3581,19 @@
         <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV17" t="n">
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3733,7 @@
         <v>14</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ18" t="n">
         <v>6</v>
@@ -3687,7 +3754,7 @@
         <v>16</v>
       </c>
       <c r="AP18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ18" t="n">
         <v>14</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3906,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
         <v>20</v>
@@ -3863,7 +3930,7 @@
         <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO19" t="n">
         <v>14</v>
@@ -3893,7 +3960,7 @@
         <v>21</v>
       </c>
       <c r="AX19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY19" t="n">
         <v>15</v>
@@ -3905,7 +3972,7 @@
         <v>19</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
         <v>9</v>
@@ -4039,7 +4106,7 @@
         <v>14</v>
       </c>
       <c r="AL20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM20" t="n">
         <v>11</v>
@@ -4084,7 +4151,7 @@
         <v>9</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>-2.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4263,7 +4330,7 @@
         <v>24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -4427,7 +4494,7 @@
         <v>14</v>
       </c>
       <c r="AT22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU22" t="n">
         <v>25</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX22" t="n">
         <v>22</v>
@@ -4445,7 +4512,7 @@
         <v>17</v>
       </c>
       <c r="AZ22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -4564,13 +4631,13 @@
         <v>8</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>3</v>
       </c>
       <c r="AG23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH23" t="n">
         <v>24</v>
@@ -4582,7 +4649,7 @@
         <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4594,7 +4661,7 @@
         <v>4</v>
       </c>
       <c r="AO23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4825,7 @@
         <v>27</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ24" t="n">
         <v>16</v>
@@ -4800,7 +4867,7 @@
         <v>18</v>
       </c>
       <c r="AW24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
@@ -4809,10 +4876,10 @@
         <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -4970,7 +5037,7 @@
         <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -5041,40 +5108,40 @@
         <v>0.632</v>
       </c>
       <c r="H26" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I26" t="n">
         <v>36.5</v>
       </c>
       <c r="J26" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.463</v>
+        <v>0.461</v>
       </c>
       <c r="L26" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M26" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="O26" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="P26" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.768</v>
+        <v>0.766</v>
       </c>
       <c r="R26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S26" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="T26" t="n">
         <v>41.3</v>
@@ -5086,7 +5153,7 @@
         <v>12.8</v>
       </c>
       <c r="W26" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X26" t="n">
         <v>4.8</v>
@@ -5095,16 +5162,16 @@
         <v>3.9</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD26" t="n">
         <v>8</v>
@@ -5119,34 +5186,34 @@
         <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK26" t="n">
         <v>8</v>
       </c>
       <c r="AL26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM26" t="n">
         <v>13</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5155,13 +5222,13 @@
         <v>28</v>
       </c>
       <c r="AT26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
         <v>23</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
@@ -5173,16 +5240,16 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -5355,7 +5422,7 @@
         <v>20</v>
       </c>
       <c r="AZ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>4</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5501,7 +5568,7 @@
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5519,7 +5586,7 @@
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>8</v>
@@ -5546,7 +5613,7 @@
         <v>23</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -5659,16 +5726,16 @@
         <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ29" t="n">
         <v>19</v>
@@ -5698,7 +5765,7 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT29" t="n">
         <v>26</v>
@@ -5713,7 +5780,7 @@
         <v>29</v>
       </c>
       <c r="AX29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5914,7 @@
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
@@ -5895,16 +5962,16 @@
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ30" t="n">
         <v>24</v>
       </c>
       <c r="BA30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB30" t="n">
         <v>6</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6029,7 +6096,7 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI31" t="n">
         <v>20</v>
@@ -6056,7 +6123,7 @@
         <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
         <v>10</v>
@@ -6083,7 +6150,7 @@
         <v>21</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-19-2008-09</t>
+          <t>2009-03-19</t>
         </is>
       </c>
     </row>
